--- a/tame_output/ON/bt/strategyON_20230728.xlsx
+++ b/tame_output/ON/bt/strategyON_20230728.xlsx
@@ -595,26 +595,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.9%</t>
+          <t>456.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>105.3%</t>
+          <t>105.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>141.9%</t>
+          <t>141.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1375,11 +1375,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>136.3%</t>
+          <t>136.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1671"/>
+  <dimension ref="A1:G1672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39943,7 +39943,7 @@
         <v>45133</v>
       </c>
       <c r="B1671" t="n">
-        <v>2.885238654138422</v>
+        <v>2.884786919010459</v>
       </c>
       <c r="C1671" t="n">
         <v>3.014274190562314</v>
@@ -39959,6 +39959,29 @@
       </c>
       <c r="G1671" t="n">
         <v>4.290946311516631</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="2" t="n">
+        <v>45134</v>
+      </c>
+      <c r="B1672" t="n">
+        <v>2.879364175590628</v>
+      </c>
+      <c r="C1672" t="n">
+        <v>3.013863868964772</v>
+      </c>
+      <c r="D1672" t="n">
+        <v>1.523528983298492</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>3.622919037970422</v>
+      </c>
+      <c r="F1672" t="n">
+        <v>2.127577848729345</v>
+      </c>
+      <c r="G1672" t="n">
+        <v>4.290410578202381</v>
       </c>
     </row>
   </sheetData>
